--- a/data/credit_bond_all_2026-10-23.xlsx
+++ b/data/credit_bond_all_2026-10-23.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-28" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-29" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-28</t>
+          <t>数据来源：DM    2026-10-29</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 22.55</t>
+          <t>C- 24.10</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C+ 32.50</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1553,7 +1553,7 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C- 19.66</t>
+          <t>C- 21.59</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 23.57</t>
+          <t>C 26.67</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 17.78</t>
+          <t>C- 18.15</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 35.05</t>
+          <t>C+ 34.18</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.35</t>
+          <t>C+ 31.00</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C 25.25</t>
+          <t>C 28.10</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 22.07</t>
+          <t>C- 22.48</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 35.82</t>
+          <t>B- 40.19</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.67</t>
+          <t>B- 38.14</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 41.82</t>
+          <t>B- 41.64</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.80</t>
+          <t>B- 35.11</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.80</t>
+          <t>B- 35.11</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B 50.51</t>
+          <t>B- 47.95</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 44.29</t>
+          <t>B- 44.05</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C 26.32</t>
+          <t>C 27.45</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C 26.32</t>
+          <t>C 27.45</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 12.76</t>
+          <t>C- 12.63</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7405,7 +7405,7 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
@@ -7637,7 +7637,7 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.21</t>
+          <t>B+ 57.02</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.21</t>
+          <t>B+ 57.02</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 24.98</t>
+          <t>C+ 30.69</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6300/1.6100</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.17</t>
+          <t>C+ 35.00</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>S- 88.33</t>
+          <t>S 90.49</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>S- 88.33</t>
+          <t>S 90.49</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4700/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 16.38</t>
+          <t>C- 13.88</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 15.12</t>
+          <t>C- 16.35</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.80</t>
+          <t>B- 35.11</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 20.65</t>
+          <t>C- 24.57</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 21.92</t>
+          <t>C- 18.10</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 21.92</t>
+          <t>C- 18.10</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="AL49" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AM49" s="3" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C- 23.64</t>
+          <t>C- 23.75</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>B- 42.06</t>
+          <t>B- 42.33</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12459,7 +12459,7 @@
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C- 19.00</t>
+          <t>C- 24.00</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>B- 40.84</t>
+          <t>B- 46.69</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C- 24.01</t>
+          <t>C+ 30.15</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>B- 44.29</t>
+          <t>B- 44.05</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 10.58</t>
+          <t>C- 10.98</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>B- 37.50</t>
+          <t>B- 37.22</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C 25.25</t>
+          <t>C 28.10</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>B- 37.02</t>
+          <t>C+ 34.20</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>B 50.51</t>
+          <t>B- 47.95</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.72</t>
+          <t>C+ 33.31</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>C- 25.00</t>
+          <t>C+ 32.86</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>B- 41.63</t>
+          <t>B- 40.13</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.32</t>
+          <t>B- 41.64</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>C- 20.65</t>
+          <t>C- 24.57</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17639,7 +17639,7 @@
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.35</t>
+          <t>C- 12.50</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17883,7 +17883,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.35</t>
+          <t>C- 12.50</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -18127,7 +18127,7 @@
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.29</t>
+          <t>C+ 33.68</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -18451,7 +18451,7 @@
       <c r="AK78" s="3"/>
       <c r="AL78" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AM78" s="3" t="inlineStr">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>C- 24.73</t>
+          <t>C 25.63</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="AL79" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AM79" s="3" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>B- 35.36</t>
+          <t>C 28.47</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -19155,7 +19155,7 @@
       <c r="AK81" s="3"/>
       <c r="AL81" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AM81" s="3" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>B- 41.79</t>
+          <t>B- 40.08</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-10-23.xlsx
+++ b/data/credit_bond_all_2026-10-23.xlsx
@@ -18996,74 +18996,74 @@
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26百福02</t>
+          <t>26鲁铁07</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>10-23 18:00</t>
+          <t>10-23 19:00</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>284368.SH</t>
+          <t>284286.SH</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>2.52</v>
+        <v>10.0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2.52</v>
+        <v>10.0</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>63.46</v>
+        <v>32.68</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>26百福01</t>
+          <t>26鲁铁06</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>4.50Y+2.00Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>2.0073</t>
+          <t>1.7339</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7800/1.7400</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>郴州市百福投资集团有限公司</t>
+          <t>山东铁路投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>C 28.47</t>
+          <t>C- 19.09</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -19087,38 +19087,38 @@
         </is>
       </c>
       <c r="U81" s="4" t="n">
-        <v>4.52</v>
+        <v>4.26</v>
       </c>
       <c r="V81" s="3"/>
       <c r="W81" s="3" t="inlineStr">
         <is>
-          <t>8-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>2.19%~2.29%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z81" s="3"/>
       <c r="AA81" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB81" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,仅用于偿还到期的公司债券本金[23百福02]</t>
+          <t>本期债券发行规模不超过人民币20.00亿元(含20.00亿元),募集资金扣除发行费用后拟用于偿还到期公司债券“21鲁铁G2”的本金,剩余部分将用于补充公司日常生产经营所需流动资金[21鲁铁G2]</t>
         </is>
       </c>
       <c r="AC81" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,华创证券有限责任公司,中邮证券有限责任公司</t>
+          <t>国泰海通证券股份有限公司,东方证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD81" s="3"/>
@@ -19139,7 +19139,7 @@
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>郴州市百福投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>山东铁路投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种一)</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -19149,18 +19149,18 @@
       </c>
       <c r="AJ81" s="3" t="inlineStr">
         <is>
-          <t>2033-10-27</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK81" s="3"/>
       <c r="AL81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AN81" s="3" t="inlineStr">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="AP81" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ81" s="3" t="inlineStr">
@@ -19185,22 +19185,22 @@
       </c>
       <c r="AR81" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS81" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT81" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU81" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t/>
         </is>
       </c>
       <c r="AV81" s="3" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="AW81" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX81" s="3" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26鲁铁07</t>
+          <t>26鲁铁08</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -19238,12 +19238,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>284286.SH</t>
+          <t>284287.SH</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -19254,18 +19254,18 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>32.68</v>
+        <v>50.0</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
@@ -19319,7 +19319,7 @@
         </is>
       </c>
       <c r="U82" s="4" t="n">
-        <v>4.26</v>
+        <v>3.21</v>
       </c>
       <c r="V82" s="3"/>
       <c r="W82" s="3" t="inlineStr">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>2.08%~2.18%</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,东方证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中泰证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中泰证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>山东铁路投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种一)</t>
+          <t>山东铁路投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种二)</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="AJ82" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t>2036-10-27</t>
         </is>
       </c>
       <c r="AK82" s="3"/>
@@ -19460,7 +19460,7 @@
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26鲁铁08</t>
+          <t>26信投Y4</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -19470,64 +19470,64 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>284287.SH</t>
+          <t>245843.SH</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H83" s="4" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>50.0</v>
+        <v>39.68</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>26鲁铁06</t>
+          <t>22信投C6</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>178D</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1.7339</t>
+          <t>1.4003</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>1.7800/1.7400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>山东铁路投资控股集团有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>C- 19.09</t>
+          <t>B- 40.08</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19551,17 +19551,17 @@
         </is>
       </c>
       <c r="U83" s="4" t="n">
-        <v>3.21</v>
+        <v>3.5667</v>
       </c>
       <c r="V83" s="3"/>
       <c r="W83" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>2.08%~2.18%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
@@ -19569,31 +19569,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z83" s="3"/>
+      <c r="Z83" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA83" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过人民币20.00亿元(含20.00亿元),募集资金扣除发行费用后拟用于偿还到期公司债券“21鲁铁G2”的本金,剩余部分将用于补充公司日常生产经营所需流动资金[21鲁铁G2]</t>
+          <t>本期债券募集资金扣除发行费用后，拟用于偿还到期或回售的公司债券本金【23 信投C6 】、【23 信投C8 】</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中泰证券股份有限公司,东方证券股份有限公司</t>
+          <t>广发证券股份有限公司,兴业证券股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD83" s="3"/>
       <c r="AE83" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司次级债</t>
         </is>
       </c>
       <c r="AF83" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG83" s="3" t="inlineStr">
@@ -19603,17 +19607,17 @@
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>山东铁路投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种二)</t>
+          <t>中信建投证券股份有限公司2026年面向专业投资者公开发行永续次级债券(第四期)</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ83" s="3" t="inlineStr">
         <is>
-          <t>2036-10-27</t>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AK83" s="3"/>
@@ -19624,7 +19628,7 @@
       </c>
       <c r="AM83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AN83" s="3" t="inlineStr">
@@ -19634,32 +19638,32 @@
       </c>
       <c r="AO83" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP83" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ83" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT83" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU83" s="3" t="inlineStr">
@@ -19674,12 +19678,12 @@
       </c>
       <c r="AW83" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX83" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY83" s="3" t="inlineStr">
@@ -19692,59 +19696,59 @@
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26信投Y4</t>
+          <t>26百福02</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>10-23 19:00</t>
+          <t>10-23 18:00</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>245843.SH</t>
+          <t>284368.SH</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>30.0</v>
+        <v>2.52</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>15.0</v>
+        <v>2.52</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>39.68</v>
+        <v>63.46</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>22信投C6</t>
+          <t>26百福01</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>178D</t>
+          <t>4.50Y+2.00Y</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>1.4003</t>
+          <t>2.0073</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -19754,12 +19758,12 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>郴州市百福投资集团有限公司</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>B- 40.08</t>
+          <t>C 28.47</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19783,53 +19787,49 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>3.5667</v>
+        <v>4.52</v>
       </c>
       <c r="V84" s="3"/>
       <c r="W84" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8-</t>
         </is>
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.19%~2.29%</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z84" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z84" s="3"/>
       <c r="AA84" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后，拟用于偿还到期或回售的公司债券本金【23 信投C6 】、【23 信投C8 】</t>
+          <t>本期公司债券募集资金扣除发行费用后,仅用于偿还到期的公司债券本金[23百福02]</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,兴业证券股份有限公司,国信证券股份有限公司</t>
+          <t>财信证券股份有限公司,华创证券有限责任公司,中邮证券有限责任公司</t>
         </is>
       </c>
       <c r="AD84" s="3"/>
       <c r="AE84" s="3" t="inlineStr">
         <is>
-          <t>证券公司次级债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF84" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG84" s="3" t="inlineStr">
@@ -19839,23 +19839,23 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司2026年面向专业投资者公开发行永续次级债券(第四期)</t>
+          <t>郴州市百福投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ84" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
+          <t>2033-10-27</t>
         </is>
       </c>
       <c r="AK84" s="3"/>
       <c r="AL84" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AM84" s="3" t="inlineStr">
@@ -19870,37 +19870,37 @@
       </c>
       <c r="AO84" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP84" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ84" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR84" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS84" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT84" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU84" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-27</t>
         </is>
       </c>
       <c r="AV84" s="3" t="inlineStr">
@@ -19910,12 +19910,12 @@
       </c>
       <c r="AW84" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX84" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY84" s="3" t="inlineStr">
